--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91470</v>
+        <v>91476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128627451</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128627453</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91476</v>
+        <v>91482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128627453</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128627451</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128627453</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128627453</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128627451</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128627453</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128627451</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128627453</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128627453</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 44878-2024 artfynd.xlsx
+++ b/artfynd/A 44878-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128627452</v>
       </c>
       <c r="B2" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128627453</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
